--- a/metadata/atacseq/todo/Stanford TMC (ATACseq).xlsx
+++ b/metadata/atacseq/todo/Stanford TMC (ATACseq).xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,7 +515,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10X Genomics; Visium Spatial Gene Expression Slide and Reagent Kit, 4 slides, 16 reactions; PN 1000184</t>
+          <t>10x Genomics; Chromium Next GEM Single Cell Fixed RNA Sample Preparation Kit, 16 rxns; PN 1000414</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -552,12 +552,12 @@
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>Parse Biosciences; Evercode WT v2 Kit, 48 rxns; PN ECW02030</t>
+          <t>10X Genomics; Visium Spatial Gene Expression Slide and Reagent Kit, 4 slides, 16 reactions; PN 1000184</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>10X Genomics; Chromium Next GEM Chip K Single Cell Kit, 48 rxns; PN 1000286</t>
+          <t>10x Genomics; Visium HD, Mouse Transcriptome, 6.5 mm, 4 runs; PN 1000676</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -589,12 +589,12 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>10X Genomics; Chromium Next GEM Single Cell 5' Kit v2, 16 rxns; PN 1000263</t>
+          <t>Parse Biosciences; Evercode WT v2 Kit, 48 rxns; PN ECW02030</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>10x Genomics; Chromium Chip E Single Cell ATAC Kit, 48 rxns; PN 1000155</t>
+          <t>10X Genomics; Chromium Next GEM Chip K Single Cell Kit, 48 rxns; PN 1000286</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>10X Genomics; Visium Spatial for FFPE Gene Expression Kit, Human Transcriptome, 1 slides, 4 reactions; PN 1000338</t>
+          <t>10X Genomics; Chromium Next GEM Single Cell 5' Kit v2, 16 rxns; PN 1000263</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>10X Genomics; Chromium Next GEM Chip G Single Cell Kit, 48 rxns; PN 1000120</t>
+          <t>10x Genomics; Chromium Chip E Single Cell ATAC Kit, 48 rxns; PN 1000155</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -648,12 +648,12 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>10X Genomics; Chromium Next GEM Single Cell 3' Kit v3.1, 16 rxns; PN 1000268</t>
+          <t>10X Genomics; Visium Spatial for FFPE Gene Expression Kit, Human Transcriptome, 1 slides, 4 reactions; PN 1000338</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>10X Genomics; Chromium Next GEM Chip G Single Cell Kit, 48 rxns; PN 1000120</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -675,12 +675,12 @@
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>10x Genomics; Chromium Next GEM Single Cell ATAC Library &amp; Gel Bead Kit, 16 rxns; PN 1000175</t>
+          <t>10X Genomics; Chromium Next GEM Single Cell 3' Kit v3.1, 16 rxns; PN 1000268</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>10X Genomics; Chromium Next GEM Chip K Single Cell Kit, 16 rxns; PN 1000287</t>
+          <t>Custom</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -697,12 +697,12 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>10x Genomics; Library Construction Kit C, 16 rxns; PN 1000694</t>
+          <t>10x Genomics; Chromium Next GEM Single Cell ATAC Library &amp; Gel Bead Kit, 16 rxns; PN 1000175</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>10X Genomics; Chromium Next GEM Chip G Single Cell Kit, 16 rxns; PN 1000127</t>
+          <t>10x Genomics; Visium HD, Human Transcriptome, 6.5 mm, 4 runs; PN 1000675</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -719,12 +719,12 @@
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>10x Genomics; Visium CytAssist Spatial Gene Expression for FFPE, Mouse Transcriptome, 6.5mm, 4 rxns; PN 1000521</t>
+          <t>10x Genomics; Library Construction Kit C, 16 rxns; PN 1000694</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>10X Genomics; Chromium NextGem Single Cell Multiome ATAC + Gene Expression Reagent Bundle, 16 rxn; PN 1000283</t>
+          <t>10X Genomics; Chromium Next GEM Chip K Single Cell Kit, 16 rxns; PN 1000287</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -741,12 +741,12 @@
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>10X Genomics; Chromium Next GEM Single Cell 3' HT Kit v3.1, 48 rxns; PN 1000348</t>
+          <t>10x Genomics; Visium CytAssist Spatial Gene Expression for FFPE, Mouse Transcriptome, 6.5mm, 4 rxns; PN 1000521</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>10x Genomics; Chromium GEM-X Single Cell 3' Kit v4, 16 rxns; PN 1000691</t>
+          <t>10X Genomics; Chromium Next GEM Chip G Single Cell Kit, 16 rxns; PN 1000127</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -763,12 +763,12 @@
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>10X Genomics; Chromium Next GEM Single Cell 3' GEM, Library &amp; Gel Bead Kit v3.1, 16 rxns; PN 1000121</t>
+          <t>10X Genomics; Chromium Next GEM Single Cell 3' HT Kit v3.1, 48 rxns; PN 1000348</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>10X Genomics; Visium FFPE Reagent Kit v2-Small, PN 1000436</t>
+          <t>10X Genomics; Chromium NextGem Single Cell Multiome ATAC + Gene Expression Reagent Bundle, 16 rxn; PN 1000283</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -785,12 +785,12 @@
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>10x Genomics; Library Construction Kit C, 4 rxns; PN 1000689</t>
+          <t>10X Genomics; Chromium Next GEM Single Cell 3' GEM, Library &amp; Gel Bead Kit v3.1, 16 rxns; PN 1000121</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>10X Genomics; Chromium Next GEM Chip Q Single Cell Kit, 16 rxns; PN 1000422</t>
+          <t>10x Genomics; Visium HD, Human Transcriptome, 11 mm, 4 runs; PN 1001037</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -807,7 +807,12 @@
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>10X Genomics; Visium CytAssist Spatial Gene Expression for FFPE, Human Transcriptome, 11 mm, 2 reactions; PN 1000522</t>
+          <t>10x Genomics; Library Construction Kit C, 4 rxns; PN 1000689</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>10x Genomics; Chromium GEM-X Single Cell 3' Kit v4, 16 rxns; PN 1000691</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -824,7 +829,12 @@
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>Illumina; TruSeq Stranded mRNA Library Prep (48 samples); PN 20020594</t>
+          <t>10X Genomics; Visium CytAssist Spatial Gene Expression for FFPE, Human Transcriptome, 11 mm, 2 reactions; PN 1000522</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>10X Genomics; Visium FFPE Reagent Kit v2-Small, PN 1000436</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -841,7 +851,12 @@
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>10X Genomics; Automated Library Construction Kit, 24 rxns; PN 1000428</t>
+          <t>Illumina; TruSeq Stranded mRNA Library Prep (48 samples); PN 20020594</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>10X Genomics; Chromium Next GEM Chip Q Single Cell Kit, 16 rxns; PN 1000422</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -858,7 +873,12 @@
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>New England BioLabs; NEBNext Ultra II RNA Library Prep Kit for Illumina; PN E7770</t>
+          <t>10X Genomics; Automated Library Construction Kit, 24 rxns; PN 1000428</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>10x Genomics; GEM-X Flex Gene Expression Chip Kit, 4 chips; PN 1000791</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -875,7 +895,12 @@
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>10X Genomics; Chromium Next GEM Automated Single Cell 5' Kit v2, 24 rxns; PN 1000290</t>
+          <t>New England BioLabs; NEBNext Ultra II RNA Library Prep Kit for Illumina; PN E7770</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>10x Genomics; Visium HD, Mouse Transcriptome, 11 mm, 4 runs; PN 1001038</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -892,7 +917,7 @@
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>10X Genomics; Visium Spatial Gene Expression Slide and Reagent Kit, 1 slides, 4 reactions; PN 1000187</t>
+          <t>10X Genomics; Chromium Next GEM Automated Single Cell 5' Kit v2, 24 rxns; PN 1000290</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -909,7 +934,7 @@
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>10x Genomics; Chromium GEM-X Single Cell 5' Kit v3, 16 rxns; PN 1000699</t>
+          <t>10X Genomics; Visium Spatial Gene Expression Slide and Reagent Kit, 1 slides, 4 reactions; PN 1000187</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -921,7 +946,7 @@
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>10x Genomics; Chromium Single Cell ATAC Library &amp; Gel Bead Kit, 16 rxns; PN 1000110</t>
+          <t>10x Genomics; Chromium GEM-X Single Cell 5' Kit v3, 16 rxns; PN 1000699</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -933,7 +958,7 @@
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
-          <t>10x Genomics; Library Construction Kit, 16 rxns; PN 1000190</t>
+          <t>10x Genomics; Chromium Single Cell ATAC Library &amp; Gel Bead Kit, 16 rxns; PN 1000110</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -945,7 +970,7 @@
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>Parse Biosciences; Evercode WT Mini v2 Kit, 12 rxns; PN ECW02010</t>
+          <t>10x Genomics; Library Construction Kit, 16 rxns; PN 1000190</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -957,7 +982,7 @@
     <row r="24">
       <c r="B24" t="inlineStr">
         <is>
-          <t>10x Genomics; Chromium Next GEM Single Cell 5' HT Kit v2, 48 rxns; PN 1000356</t>
+          <t>Parse Biosciences; Evercode WT Mini v2 Kit, 12 rxns; PN ECW02010</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -969,7 +994,7 @@
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>Illumina; TruSeq Stranded mRNA Library Prep (96 samples); PN 20020595</t>
+          <t>10x Genomics; Chromium Next GEM Single Cell 5' HT Kit v2, 48 rxns; PN 1000356</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -981,7 +1006,7 @@
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
-          <t>10X Genomics; Chromium Next GEM Single Cell 5' Kit v2, 4 rxns; PN 1000265</t>
+          <t>Illumina; TruSeq Stranded mRNA Library Prep (96 samples); PN 20020595</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -993,7 +1018,7 @@
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
-          <t>10X Genomics; Chromium NextGem Single Cell Multiome ATAC + Gene Expression Reagent Bundle, 4 rxn; PN 1000285</t>
+          <t>10X Genomics; Chromium Next GEM Single Cell 5' Kit v2, 4 rxns; PN 1000265</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1005,7 +1030,7 @@
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>10X Genomics; Chromium Next GEM Single Cell Fixed RNA Hybridization &amp; Library Kit, 4 rxns; PN 1000415</t>
+          <t>10X Genomics; Chromium NextGem Single Cell Multiome ATAC + Gene Expression Reagent Bundle, 4 rxn; PN 1000285</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1017,7 +1042,7 @@
     <row r="29">
       <c r="B29" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>10X Genomics; Chromium Next GEM Single Cell Fixed RNA Hybridization &amp; Library Kit, 4 rxns; PN 1000415</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1029,54 +1054,75 @@
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>10X Genomics; Chromium Single Cell 3' GEM, Library &amp; Gel Bead Kit v3, 4 rxns; PN 1000092</t>
+          <t>Custom</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
         <is>
-          <t>10x Genomics; Chromium Single Cell 3ʹ GEM, Library &amp; Gel Bead Kit v3, 16 rxns; PN 1000075</t>
+          <t>10X Genomics; Chromium Single Cell 3' GEM, Library &amp; Gel Bead Kit v3, 4 rxns; PN 1000092</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="inlineStr">
         <is>
-          <t>10X Genomics; Chromium Single Cell 3' Library &amp; Gel Bead Kit, 4 rxns; PN 120267</t>
+          <t>10x Genomics; Chromium Single Cell 3ʹ GEM, Library &amp; Gel Bead Kit v3, 16 rxns; PN 1000075</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="inlineStr">
         <is>
-          <t>10X Genomics; Visium Spatial for FFPE Gene Expression Kit, Mouse Transcriptome, 4 rxns; PN 1000339</t>
+          <t>10X Genomics; Chromium Single Cell 3' Library &amp; Gel Bead Kit, 4 rxns; PN 120267</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="inlineStr">
         <is>
-          <t>10X Genomics; Chromium NextGem Single Cell Multiome ATAC + Gene Expression Reagent Bundle, 16 rxn; PN 1000283</t>
+          <t>10X Genomics; Visium Spatial for FFPE Gene Expression Kit, Mouse Transcriptome, 4 rxns; PN 1000339</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="inlineStr">
         <is>
-          <t>10X Genomics; Chromium Next GEM Single Cell 3' Kit v3.1, 4 rxns; PN 1000269</t>
+          <t>10X Genomics; Chromium NextGem Single Cell Multiome ATAC + Gene Expression Reagent Bundle, 16 rxn; PN 1000283</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="inlineStr">
         <is>
-          <t>10x Genomics; Chromium Next GEM Single Cell 5' HT Kit v2, 8 rxns; PN 1000374</t>
+          <t>Epigenome Technologies; Multiplex Droplet Paired-Tag 16 Reaction Kit; PN MDP16101</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="inlineStr">
+        <is>
+          <t>10X Genomics; Chromium Next GEM Single Cell 3' Kit v3.1, 4 rxns; PN 1000269</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>10x Genomics; GEM-X Flex GEM &amp; Library Kit, 4 rxns; PN 1000782</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>10x Genomics; Chromium Next GEM Single Cell 5' HT Kit v2, 8 rxns; PN 1000374</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
         <is>
           <t>10X Genomics; Visium CytAssist Spatial Gene Expression for FFPE, Human Transcriptome, 6.5mm, 4 reactions; PN 1000520</t>
         </is>
@@ -1136,7 +1182,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -1205,7 +1251,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -1251,7 +1297,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1297,7 +1343,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -1366,7 +1412,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -1412,7 +1458,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1458,7 +1504,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1550,7 +1596,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1619,7 +1665,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1711,7 +1757,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1780,7 +1826,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1826,7 +1872,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1895,7 +1941,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1987,7 +2033,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -2033,7 +2079,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -2148,7 +2194,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -2217,7 +2263,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -2286,7 +2332,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -2332,7 +2378,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -2424,7 +2470,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -2493,7 +2539,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -2562,7 +2608,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -2608,7 +2654,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2677,7 +2723,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -2769,7 +2815,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -2815,7 +2861,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -2907,7 +2953,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -2976,7 +3022,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -3068,7 +3114,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -3137,7 +3183,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -3183,7 +3229,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -3252,7 +3298,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -3344,7 +3390,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -3436,7 +3482,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -3482,7 +3528,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -3551,7 +3597,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -3620,7 +3666,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
@@ -3712,7 +3758,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
@@ -3781,7 +3827,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -3850,7 +3896,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -3919,7 +3965,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -3988,7 +4034,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -4080,7 +4126,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
@@ -4172,7 +4218,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
@@ -4218,7 +4264,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
@@ -4287,7 +4333,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
@@ -4379,7 +4425,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -4471,7 +4517,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -4609,7 +4655,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
@@ -4678,7 +4724,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
@@ -4747,7 +4793,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -4816,7 +4862,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
@@ -4862,7 +4908,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -4931,7 +4977,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
@@ -5000,7 +5046,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
@@ -5092,7 +5138,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -5161,7 +5207,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -5207,7 +5253,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
@@ -5299,7 +5345,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
@@ -5345,7 +5391,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -5437,7 +5483,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
@@ -5506,7 +5552,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -5598,7 +5644,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
@@ -5644,7 +5690,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
@@ -5713,7 +5759,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
@@ -5782,7 +5828,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
@@ -5828,7 +5874,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
@@ -5920,7 +5966,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
@@ -5989,7 +6035,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -6081,7 +6127,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
@@ -6124,13 +6170,13 @@
       <formula1>_validation_data!$G$1:$G$4</formula1>
     </dataValidation>
     <dataValidation sqref="D4 D11 D38 D45 D48 D57 D60 D72 D78 D81 D85 D88 D101 D113 D116 D129 D133 D146 D152 D155 D158 D161 D182 D188 D191 D195 D216" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="List Selection" prompt="Please select from the list" type="list">
-      <formula1>_validation_data!$C$1:$C$13</formula1>
+      <formula1>_validation_data!$C$1:$C$18</formula1>
     </dataValidation>
     <dataValidation sqref="D18 D22 D25 D29 D34 D37 D43 D56 D68 D71 D77 D93 D96 D100 D106 D109 D112 D122 D125 D128 D138 D141 D145 D166 D169 D172 D176 D181 D187 D200 D203 D208 D212 D215" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="List Selection" prompt="Please select from the list" type="list">
       <formula1>_validation_data!$H$1:$H$7</formula1>
     </dataValidation>
     <dataValidation sqref="D19 D26 D44 D51 D63 D84 D97 D119 D132 D142 D149 D150 D151 D173 D194 D209" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="List Selection" prompt="Please select from the list" type="list">
-      <formula1>_validation_data!$B$1:$B$37</formula1>
+      <formula1>_validation_data!$B$1:$B$40</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15787,7 +15833,7 @@
       <formula1>_validation_data!$A$1:$A$3</formula1>
     </dataValidation>
     <dataValidation sqref="C4 C16 C23 C36 C43 C56 C63 C76 C83 C90 C97 C109 C138 C145 C169 C176 C183 C195 C228 C235 C248 C260 C267 C274 C297 C304 C311 C334 C341 C354 C404 C411 C418 C431 C438 C445 C457 C485 C492 C499 C506 C519 C526" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="List Selection" prompt="Please select from the list" type="list">
-      <formula1>_validation_data!$B$1:$B$37</formula1>
+      <formula1>_validation_data!$B$1:$B$40</formula1>
     </dataValidation>
     <dataValidation sqref="C5 C17 C24 C37 C44 C50 C57 C64 C70 C77 C84 C91 C98 C110 C116 C132 C139 C146 C163 C170 C177 C184 C196 C212 C229 C236 C242 C249 C261 C268 C275 C291 C298 C305 C312 C323 C335 C342 C348 C355 C366 C372 C378 C405 C412 C419 C425 C432 C439 C446 C458 C474 C486 C493 C500 C507 C513 C520 C527" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="List Selection" prompt="Please select from the list" type="list">
       <formula1>_validation_data!$D$1:$D$19</formula1>
